--- a/data/inflation.xlsx
+++ b/data/inflation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frederick Duff\Desktop\Real Estate Project\FORECAST\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Real estate Forecast\RealEstateAI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0779AB9-E5E0-4E68-A353-2DD13D0C2BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4605D215-FBA7-4CC9-8F2F-60C13CF57DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{9C3F75CC-EF30-4873-A10D-A4A6E40F37D9}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9C3F75CC-EF30-4873-A10D-A4A6E40F37D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -72,7 +72,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -82,12 +82,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -105,7 +99,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -113,19 +107,12 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{E06774AC-42D0-43A5-B8A8-3813AE616529}"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.14996795556505021"/>
-      </font>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color theme="0" tint="-0.14996795556505021"/>
@@ -466,16 +453,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE5A24B-9BEA-4A64-B1BB-17BC1CC0E751}">
-  <dimension ref="A1:D195"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:D197"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.68359375" customWidth="1"/>
-    <col min="3" max="3" width="14.83984375" customWidth="1"/>
-    <col min="4" max="4" width="11.68359375" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -489,7 +476,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>40179</v>
       </c>
@@ -503,7 +490,7 @@
         <v>71.400000000000006</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>40210</v>
       </c>
@@ -517,7 +504,7 @@
         <v>73.5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>40238</v>
       </c>
@@ -531,7 +518,7 @@
         <v>73.900000000000006</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>40269</v>
       </c>
@@ -545,7 +532,7 @@
         <v>73.099999999999994</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>40299</v>
       </c>
@@ -559,7 +546,7 @@
         <v>73.099999999999994</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>40330</v>
       </c>
@@ -573,7 +560,7 @@
         <v>73.900000000000006</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>40360</v>
       </c>
@@ -587,7 +574,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>40391</v>
       </c>
@@ -601,7 +588,7 @@
         <v>70.900000000000006</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>40422</v>
       </c>
@@ -615,7 +602,7 @@
         <v>68.3</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>40452</v>
       </c>
@@ -629,7 +616,7 @@
         <v>68.3</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>40483</v>
       </c>
@@ -643,7 +630,7 @@
         <v>69.2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>40513</v>
       </c>
@@ -657,7 +644,7 @@
         <v>71.3</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>40544</v>
       </c>
@@ -671,7 +658,7 @@
         <v>73.400000000000006</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>40575</v>
       </c>
@@ -685,7 +672,7 @@
         <v>75.400000000000006</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>40603</v>
       </c>
@@ -699,7 +686,7 @@
         <v>73.099999999999994</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>40634</v>
       </c>
@@ -713,7 +700,7 @@
         <v>71.599999999999994</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>40664</v>
       </c>
@@ -727,7 +714,7 @@
         <v>70.5</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>40695</v>
       </c>
@@ -741,7 +728,7 @@
         <v>71.900000000000006</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>40725</v>
       </c>
@@ -755,7 +742,7 @@
         <v>69.8</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>40756</v>
       </c>
@@ -769,7 +756,7 @@
         <v>63.7</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>40787</v>
       </c>
@@ -783,7 +770,7 @@
         <v>59.7</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>40817</v>
       </c>
@@ -797,7 +784,7 @@
         <v>58.7</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>40848</v>
       </c>
@@ -811,7 +798,7 @@
         <v>61.3</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>40878</v>
       </c>
@@ -825,7 +812,7 @@
         <v>64.8</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>40909</v>
       </c>
@@ -839,7 +826,7 @@
         <v>69.5</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>40940</v>
       </c>
@@ -853,7 +840,7 @@
         <v>73.400000000000006</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>40969</v>
       </c>
@@ -867,7 +854,7 @@
         <v>75.5</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>41000</v>
       </c>
@@ -881,7 +868,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>41030</v>
       </c>
@@ -895,7 +882,7 @@
         <v>77.3</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>41061</v>
       </c>
@@ -909,7 +896,7 @@
         <v>76.3</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>41091</v>
       </c>
@@ -923,7 +910,7 @@
         <v>74.900000000000006</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>41122</v>
       </c>
@@ -937,7 +924,7 @@
         <v>73.3</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>41153</v>
       </c>
@@ -951,7 +938,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>41183</v>
       </c>
@@ -965,7 +952,7 @@
         <v>78.400000000000006</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>41214</v>
       </c>
@@ -979,7 +966,7 @@
         <v>81.2</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>41244</v>
       </c>
@@ -993,7 +980,7 @@
         <v>79.400000000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>41275</v>
       </c>
@@ -1007,7 +994,7 @@
         <v>76.5</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>41306</v>
       </c>
@@ -1021,7 +1008,7 @@
         <v>74.8</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>41334</v>
       </c>
@@ -1035,7 +1022,7 @@
         <v>76.7</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>41365</v>
       </c>
@@ -1049,7 +1036,7 @@
         <v>77.5</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>41395</v>
       </c>
@@ -1063,7 +1050,7 @@
         <v>79.8</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>41426</v>
       </c>
@@ -1077,7 +1064,7 @@
         <v>81.7</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>41456</v>
       </c>
@@ -1091,7 +1078,7 @@
         <v>84.6</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>41487</v>
       </c>
@@ -1105,7 +1092,7 @@
         <v>83.8</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>41518</v>
       </c>
@@ -1119,7 +1106,7 @@
         <v>81.599999999999994</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>41548</v>
       </c>
@@ -1133,7 +1120,7 @@
         <v>77.599999999999994</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>41579</v>
       </c>
@@ -1147,7 +1134,7 @@
         <v>75.3</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>41609</v>
       </c>
@@ -1161,7 +1148,7 @@
         <v>76.900000000000006</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>41640</v>
       </c>
@@ -1175,7 +1162,7 @@
         <v>79.599999999999994</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>41671</v>
       </c>
@@ -1189,7 +1176,7 @@
         <v>81.8</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>41699</v>
       </c>
@@ -1203,7 +1190,7 @@
         <v>80.900000000000006</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>41730</v>
       </c>
@@ -1217,7 +1204,7 @@
         <v>81.900000000000006</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>41760</v>
       </c>
@@ -1231,7 +1218,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>41791</v>
       </c>
@@ -1245,7 +1232,7 @@
         <v>82.8</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>41821</v>
       </c>
@@ -1259,7 +1246,7 @@
         <v>82.1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>41852</v>
       </c>
@@ -1273,7 +1260,7 @@
         <v>82.3</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>41883</v>
       </c>
@@ -1287,7 +1274,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>41913</v>
       </c>
@@ -1301,7 +1288,7 @@
         <v>84.7</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>41944</v>
       </c>
@@ -1315,7 +1302,7 @@
         <v>86.8</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>41974</v>
       </c>
@@ -1329,7 +1316,7 @@
         <v>89.8</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>42005</v>
       </c>
@@ -1343,7 +1330,7 @@
         <v>93.5</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>42036</v>
       </c>
@@ -1357,7 +1344,7 @@
         <v>95.7</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>42064</v>
       </c>
@@ -1371,7 +1358,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>42095</v>
       </c>
@@ -1385,7 +1372,7 @@
         <v>94.8</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>42125</v>
       </c>
@@ -1399,7 +1386,7 @@
         <v>93.2</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>42156</v>
       </c>
@@ -1413,7 +1400,7 @@
         <v>94.2</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>42186</v>
       </c>
@@ -1427,7 +1414,7 @@
         <v>93.3</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>42217</v>
       </c>
@@ -1441,7 +1428,7 @@
         <v>93.7</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>42248</v>
       </c>
@@ -1455,7 +1442,7 @@
         <v>90.7</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>42278</v>
       </c>
@@ -1469,7 +1456,7 @@
         <v>89.7</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>42309</v>
       </c>
@@ -1483,7 +1470,7 @@
         <v>89.5</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>42339</v>
       </c>
@@ -1497,7 +1484,7 @@
         <v>91.3</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>42370</v>
       </c>
@@ -1511,7 +1498,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>42401</v>
       </c>
@@ -1525,7 +1512,7 @@
         <v>92.1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>42430</v>
       </c>
@@ -1539,7 +1526,7 @@
         <v>91.6</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>42461</v>
       </c>
@@ -1553,7 +1540,7 @@
         <v>90.6</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>42491</v>
       </c>
@@ -1567,7 +1554,7 @@
         <v>91.6</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>42522</v>
       </c>
@@ -1581,7 +1568,7 @@
         <v>92.4</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>42552</v>
       </c>
@@ -1595,7 +1582,7 @@
         <v>92.7</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>42583</v>
       </c>
@@ -1609,7 +1596,7 @@
         <v>91.1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>42614</v>
       </c>
@@ -1623,7 +1610,7 @@
         <v>90.3</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>42644</v>
       </c>
@@ -1637,7 +1624,7 @@
         <v>89.4</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>42675</v>
       </c>
@@ -1651,7 +1638,7 @@
         <v>90.7</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>42705</v>
       </c>
@@ -1665,7 +1652,7 @@
         <v>93.1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>42736</v>
       </c>
@@ -1679,7 +1666,7 @@
         <v>96.8</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>42767</v>
       </c>
@@ -1693,7 +1680,7 @@
         <v>97.7</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>42795</v>
       </c>
@@ -1707,7 +1694,7 @@
         <v>97.2</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>42826</v>
       </c>
@@ -1721,7 +1708,7 @@
         <v>96.7</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>42856</v>
       </c>
@@ -1735,7 +1722,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>42887</v>
       </c>
@@ -1749,7 +1736,7 @@
         <v>96.4</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>42917</v>
       </c>
@@ -1763,7 +1750,7 @@
         <v>95.2</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>42948</v>
       </c>
@@ -1777,7 +1764,7 @@
         <v>95.1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>42979</v>
       </c>
@@ -1791,7 +1778,7 @@
         <v>95.1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>43009</v>
       </c>
@@ -1805,7 +1792,7 @@
         <v>97.5</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>43040</v>
       </c>
@@ -1819,7 +1806,7 @@
         <v>98.1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>43070</v>
       </c>
@@ -1833,7 +1820,7 @@
         <v>98.4</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>43101</v>
       </c>
@@ -1847,7 +1834,7 @@
         <v>96.7</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>43132</v>
       </c>
@@ -1861,7 +1848,7 @@
         <v>97.1</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>43160</v>
       </c>
@@ -1875,7 +1862,7 @@
         <v>98.9</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>43191</v>
       </c>
@@ -1889,7 +1876,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>43221</v>
       </c>
@@ -1903,7 +1890,7 @@
         <v>99.4</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>43252</v>
       </c>
@@ -1917,7 +1904,7 @@
         <v>98.3</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>43282</v>
       </c>
@@ -1931,7 +1918,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>43313</v>
       </c>
@@ -1945,7 +1932,7 @@
         <v>97.4</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>43344</v>
       </c>
@@ -1959,7 +1946,7 @@
         <v>98.1</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>43374</v>
       </c>
@@ -1973,7 +1960,7 @@
         <v>98.3</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>43405</v>
       </c>
@@ -1987,7 +1974,7 @@
         <v>98.7</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>43435</v>
       </c>
@@ -2001,7 +1988,7 @@
         <v>98.1</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>43466</v>
       </c>
@@ -2015,7 +2002,7 @@
         <v>95.7</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>43497</v>
       </c>
@@ -2029,7 +2016,7 @@
         <v>94.4</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>43525</v>
       </c>
@@ -2043,7 +2030,7 @@
         <v>94.5</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>43556</v>
       </c>
@@ -2057,7 +2044,7 @@
         <v>96.5</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>43586</v>
       </c>
@@ -2071,7 +2058,7 @@
         <v>98.5</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>43617</v>
       </c>
@@ -2085,7 +2072,7 @@
         <v>98.5</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>43647</v>
       </c>
@@ -2099,7 +2086,7 @@
         <v>98.9</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>43678</v>
       </c>
@@ -2113,7 +2100,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>43709</v>
       </c>
@@ -2127,7 +2114,7 @@
         <v>93.8</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>43739</v>
       </c>
@@ -2141,7 +2128,7 @@
         <v>92.8</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>43770</v>
       </c>
@@ -2155,7 +2142,7 @@
         <v>95.2</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>43800</v>
       </c>
@@ -2169,7 +2156,7 @@
         <v>97.2</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>43831</v>
       </c>
@@ -2183,7 +2170,7 @@
         <v>98.6</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>43862</v>
       </c>
@@ -2197,7 +2184,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>43891</v>
       </c>
@@ -2211,7 +2198,7 @@
         <v>96.6</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>43922</v>
       </c>
@@ -2225,7 +2212,7 @@
         <v>87.3</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>43952</v>
       </c>
@@ -2239,7 +2226,7 @@
         <v>77.7</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>43983</v>
       </c>
@@ -2253,7 +2240,7 @@
         <v>74.099999999999994</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>44013</v>
       </c>
@@ -2267,7 +2254,7 @@
         <v>74.3</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>44044</v>
       </c>
@@ -2281,7 +2268,7 @@
         <v>74.900000000000006</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>44075</v>
       </c>
@@ -2295,7 +2282,7 @@
         <v>75.7</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>44105</v>
       </c>
@@ -2309,7 +2296,7 @@
         <v>78.8</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>44136</v>
       </c>
@@ -2323,7 +2310,7 @@
         <v>79.7</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>44166</v>
       </c>
@@ -2337,7 +2324,7 @@
         <v>79.8</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>44197</v>
       </c>
@@ -2351,7 +2338,7 @@
         <v>78.900000000000006</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>44228</v>
       </c>
@@ -2365,7 +2352,7 @@
         <v>78.8</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>44256</v>
       </c>
@@ -2379,7 +2366,7 @@
         <v>80.2</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>44287</v>
       </c>
@@ -2393,7 +2380,7 @@
         <v>83.3</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>44317</v>
       </c>
@@ -2407,7 +2394,7 @@
         <v>85.4</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>44348</v>
       </c>
@@ -2421,7 +2408,7 @@
         <v>85.6</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>44378</v>
       </c>
@@ -2435,7 +2422,7 @@
         <v>83.2</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>44409</v>
       </c>
@@ -2449,7 +2436,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>44440</v>
       </c>
@@ -2463,7 +2450,7 @@
         <v>74.8</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>44470</v>
       </c>
@@ -2477,7 +2464,7 @@
         <v>71.599999999999994</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>44501</v>
       </c>
@@ -2491,7 +2478,7 @@
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>44531</v>
       </c>
@@ -2505,7 +2492,7 @@
         <v>69.900000000000006</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>44562</v>
       </c>
@@ -2519,7 +2506,7 @@
         <v>68.400000000000006</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>44593</v>
       </c>
@@ -2533,7 +2520,7 @@
         <v>66.900000000000006</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>44621</v>
       </c>
@@ -2547,7 +2534,7 @@
         <v>63.1</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>44652</v>
       </c>
@@ -2561,7 +2548,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>44682</v>
       </c>
@@ -2575,7 +2562,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>44713</v>
       </c>
@@ -2589,7 +2576,7 @@
         <v>57.9</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>44743</v>
       </c>
@@ -2603,7 +2590,7 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>44774</v>
       </c>
@@ -2617,7 +2604,7 @@
         <v>53.2</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>44805</v>
       </c>
@@ -2631,7 +2618,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>44835</v>
       </c>
@@ -2645,7 +2632,7 @@
         <v>58.9</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>44866</v>
       </c>
@@ -2659,7 +2646,7 @@
         <v>58.4</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>44896</v>
       </c>
@@ -2673,7 +2660,7 @@
         <v>58.8</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>44927</v>
       </c>
@@ -2687,7 +2674,7 @@
         <v>60.5</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>44958</v>
       </c>
@@ -2701,7 +2688,7 @@
         <v>63.9</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>44986</v>
       </c>
@@ -2715,7 +2702,7 @@
         <v>64.599999999999994</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>45017</v>
       </c>
@@ -2729,7 +2716,7 @@
         <v>64.2</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>45047</v>
       </c>
@@ -2743,7 +2730,7 @@
         <v>61.6</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>45078</v>
       </c>
@@ -2757,7 +2744,7 @@
         <v>62.3</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>45108</v>
       </c>
@@ -2771,7 +2758,7 @@
         <v>64.900000000000006</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>45139</v>
       </c>
@@ -2785,7 +2772,7 @@
         <v>68.400000000000006</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>45170</v>
       </c>
@@ -2799,7 +2786,7 @@
         <v>69.599999999999994</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>45200</v>
       </c>
@@ -2813,7 +2800,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>45231</v>
       </c>
@@ -2827,7 +2814,7 @@
         <v>64.3</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>45261</v>
       </c>
@@ -2841,7 +2828,7 @@
         <v>64.900000000000006</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>45292</v>
       </c>
@@ -2855,7 +2842,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>45323</v>
       </c>
@@ -2869,7 +2856,7 @@
         <v>75.2</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>45352</v>
       </c>
@@ -2883,7 +2870,7 @@
         <v>78.400000000000006</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>45383</v>
       </c>
@@ -2897,7 +2884,7 @@
         <v>77.8</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>45413</v>
       </c>
@@ -2911,7 +2898,7 @@
         <v>75.2</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>45444</v>
       </c>
@@ -2925,7 +2912,7 @@
         <v>71.5</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>45474</v>
       </c>
@@ -2939,7 +2926,7 @@
         <v>67.900000000000006</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>45505</v>
       </c>
@@ -2953,7 +2940,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>45536</v>
       </c>
@@ -2967,7 +2954,7 @@
         <v>68.099999999999994</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>45566</v>
       </c>
@@ -2981,7 +2968,7 @@
         <v>69.5</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>45597</v>
       </c>
@@ -2995,7 +2982,7 @@
         <v>70.8</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>45627</v>
       </c>
@@ -3009,7 +2996,7 @@
         <v>72.099999999999994</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>45658</v>
       </c>
@@ -3023,7 +3010,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>45689</v>
       </c>
@@ -3037,7 +3024,7 @@
         <v>70.099999999999994</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>45717</v>
       </c>
@@ -3051,7 +3038,7 @@
         <v>64.5</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>45748</v>
       </c>
@@ -3065,7 +3052,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>45778</v>
       </c>
@@ -3079,7 +3066,7 @@
         <v>53.8</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>45809</v>
       </c>
@@ -3093,7 +3080,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>45839</v>
       </c>
@@ -3107,7 +3094,7 @@
         <v>58.2</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>45870</v>
       </c>
@@ -3121,7 +3108,7 @@
         <v>60.2</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>45901</v>
       </c>
@@ -3135,7 +3122,7 @@
         <v>58.3</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>45931</v>
       </c>
@@ -3149,7 +3136,7 @@
         <v>55.6</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>45962</v>
       </c>
@@ -3163,55 +3150,83 @@
         <v>53.2</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>45992</v>
       </c>
       <c r="B193" s="4">
         <v>2.6</v>
       </c>
-      <c r="C193" s="6">
+      <c r="C193" s="3">
         <v>4.4000000000000004</v>
       </c>
       <c r="D193">
         <v>52.5</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>46023</v>
       </c>
       <c r="B194" s="4">
         <v>2.4</v>
       </c>
-      <c r="C194" s="6">
+      <c r="C194" s="3">
         <v>4.3</v>
       </c>
       <c r="D194">
         <v>53.4</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>46054</v>
       </c>
-      <c r="B195" s="7">
+      <c r="B195" s="4">
         <v>2.4</v>
       </c>
-      <c r="C195" s="8">
+      <c r="C195" s="5">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D195">
+        <v>56.6</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A196" s="1">
+        <v>46082</v>
+      </c>
+      <c r="B196" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="C196" s="6">
         <v>4.3</v>
       </c>
-      <c r="D195">
-        <v>55.3</v>
+      <c r="D196">
+        <v>53.3</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A197" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B197" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="C197" s="6">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D197">
+        <v>49.8</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D140">
-    <cfRule type="containsErrors" dxfId="2" priority="2" stopIfTrue="1">
+    <cfRule type="containsErrors" dxfId="1" priority="2" stopIfTrue="1">
       <formula>ISERROR(D2)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D182:D195">
+  <conditionalFormatting sqref="D182:D197">
     <cfRule type="containsErrors" dxfId="0" priority="1" stopIfTrue="1">
       <formula>ISERROR(D182)</formula>
     </cfRule>
